--- a/output/pdf_financials_xlsx/SVI.xlsx
+++ b/output/pdf_financials_xlsx/SVI.xlsx
@@ -3334,37 +3334,37 @@
         <v>0.110139</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.087779</v>
+        <v>0.324088</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0</v>
+        <v>0.27059</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0</v>
+        <v>0.66208</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>4.798355</v>
+        <v>8.71068</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.256928</v>
+        <v>5.191801</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0</v>
+        <v>2.985805</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>2.281288</v>
+        <v>6.381806</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>3.306466</v>
+        <v>9.946491999999999</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>7.318088</v>
+        <v>15.84063</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0</v>
+        <v>9.259634</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>7.808765</v>
+        <v>17.526168</v>
       </c>
     </row>
     <row r="49">
@@ -3397,34 +3397,52 @@
         <v>1.066451</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>0.27059</v>
-      </c>
-      <c r="J49" s="3" t="n">
-        <v>0.66208</v>
-      </c>
-      <c r="K49" s="3" t="n">
-        <v>8.71068</v>
-      </c>
-      <c r="L49" s="3" t="n">
-        <v>5.191801</v>
-      </c>
-      <c r="M49" s="3" t="n">
-        <v>2.985805</v>
-      </c>
-      <c r="N49" s="3" t="n">
-        <v>6.381806</v>
-      </c>
-      <c r="O49" s="3" t="n">
-        <v>9.946491999999999</v>
-      </c>
-      <c r="P49" s="3" t="n">
-        <v>15.84063</v>
-      </c>
-      <c r="Q49" s="3" t="n">
-        <v>9.259634</v>
-      </c>
-      <c r="R49" s="3" t="n">
-        <v>17.526168</v>
+        <v>4.597061</v>
+      </c>
+      <c r="J49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -4127,34 +4145,34 @@
         <v>0</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>4.326471</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>342.141501</v>
+        <v>0</v>
       </c>
       <c r="K61" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>1017.599616</v>
+        <v>0</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>1389.880157</v>
+        <v>0</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>1829.774403</v>
+        <v>0</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>2010.805668</v>
+        <v>0</v>
       </c>
       <c r="P61" s="3" t="n">
-        <v>2028.377326</v>
+        <v>0</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>2224.708626</v>
+        <v>0</v>
       </c>
       <c r="R61" s="3" t="n">
-        <v>2389.307263</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -4199,36 +4217,52 @@
         </is>
       </c>
       <c r="I62" s="3" t="n">
-        <v>171.215887</v>
-      </c>
-      <c r="J62" s="3" t="n">
-        <v>342.141501</v>
+        <v>166.889416</v>
+      </c>
+      <c r="J62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K62" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L62" s="3" t="n">
-        <v>1017.599616</v>
-      </c>
-      <c r="M62" s="3" t="n">
-        <v>1389.880157</v>
-      </c>
-      <c r="N62" s="3" t="n">
-        <v>1829.774403</v>
-      </c>
-      <c r="O62" s="3" t="n">
-        <v>2010.805668</v>
-      </c>
-      <c r="P62" s="3" t="n">
-        <v>2028.377326</v>
-      </c>
-      <c r="Q62" s="3" t="n">
-        <v>2224.708626</v>
-      </c>
-      <c r="R62" s="3" t="n">
-        <v>2389.307263</v>
+      <c r="L62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -9072,7 +9106,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -13995,7 +14029,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -15593,7 +15627,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">

--- a/output/pdf_financials_xlsx/SVI.xlsx
+++ b/output/pdf_financials_xlsx/SVI.xlsx
@@ -2504,13 +2504,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.152024</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.311885</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.759495</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0</v>
@@ -2620,13 +2620,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>3.31176</v>
+        <v>3.463784</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.311885</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.5</v>
+        <v>1.259495</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0</v>
@@ -3334,37 +3334,37 @@
         <v>0.110139</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.324088</v>
+        <v>0.087779</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.27059</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.66208</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>8.71068</v>
+        <v>4.798355</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>5.191801</v>
+        <v>0.256928</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.985805</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>6.381806</v>
+        <v>2.281288</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>9.946491999999999</v>
+        <v>3.306466</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>15.84063</v>
+        <v>7.318088</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>9.259634</v>
+        <v>0</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>17.526168</v>
+        <v>7.808765</v>
       </c>
     </row>
     <row r="49">
@@ -3397,52 +3397,34 @@
         <v>1.066451</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>4.597061</v>
-      </c>
-      <c r="J49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.27059</v>
+      </c>
+      <c r="J49" s="3" t="n">
+        <v>0.66208</v>
+      </c>
+      <c r="K49" s="3" t="n">
+        <v>8.71068</v>
+      </c>
+      <c r="L49" s="3" t="n">
+        <v>5.191801</v>
+      </c>
+      <c r="M49" s="3" t="n">
+        <v>2.985805</v>
+      </c>
+      <c r="N49" s="3" t="n">
+        <v>6.381806</v>
+      </c>
+      <c r="O49" s="3" t="n">
+        <v>9.946491999999999</v>
+      </c>
+      <c r="P49" s="3" t="n">
+        <v>15.84063</v>
+      </c>
+      <c r="Q49" s="3" t="n">
+        <v>9.259634</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>17.526168</v>
       </c>
     </row>
     <row r="50">
@@ -4145,34 +4127,34 @@
         <v>0</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0</v>
+        <v>4.326471</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0</v>
+        <v>342.141501</v>
       </c>
       <c r="K61" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>0</v>
+        <v>1017.599616</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>0</v>
+        <v>1389.880157</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>0</v>
+        <v>1829.774403</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>0</v>
+        <v>2010.805668</v>
       </c>
       <c r="P61" s="3" t="n">
-        <v>0</v>
+        <v>2028.377326</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>0</v>
+        <v>2224.708626</v>
       </c>
       <c r="R61" s="3" t="n">
-        <v>0</v>
+        <v>2389.307263</v>
       </c>
     </row>
     <row r="62">
@@ -4217,52 +4199,36 @@
         </is>
       </c>
       <c r="I62" s="3" t="n">
-        <v>166.889416</v>
-      </c>
-      <c r="J62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>171.215887</v>
+      </c>
+      <c r="J62" s="3" t="n">
+        <v>342.141501</v>
       </c>
       <c r="K62" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L62" s="3" t="n">
+        <v>1017.599616</v>
+      </c>
+      <c r="M62" s="3" t="n">
+        <v>1389.880157</v>
+      </c>
+      <c r="N62" s="3" t="n">
+        <v>1829.774403</v>
+      </c>
+      <c r="O62" s="3" t="n">
+        <v>2010.805668</v>
+      </c>
+      <c r="P62" s="3" t="n">
+        <v>2028.377326</v>
+      </c>
+      <c r="Q62" s="3" t="n">
+        <v>2224.708626</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>2389.307263</v>
       </c>
     </row>
     <row r="63">
@@ -9106,7 +9072,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -14029,7 +13995,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -15627,7 +15593,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -23719,7 +23685,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E152" s="5" t="n">

--- a/output/pdf_financials_xlsx/SVI.xlsx
+++ b/output/pdf_financials_xlsx/SVI.xlsx
@@ -7186,16 +7186,16 @@
         <v>0</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.00318</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.04925</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.020775</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.319475</v>
       </c>
       <c r="K112" s="3" t="n">
         <v>0</v>
@@ -36343,7 +36343,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -37242,7 +37246,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -38424,7 +38432,11 @@
           <t>Additions to intangible assets (Note 6)</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr"/>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr">
         <is>
           <t>-</t>
@@ -38523,7 +38535,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>
@@ -39802,7 +39818,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
@@ -40895,7 +40915,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SVI.xlsx
+++ b/output/pdf_financials_xlsx/SVI.xlsx
@@ -4008,10 +4008,10 @@
         <v>0.008800000000000001</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>1.607814</v>
+        <v>0.0064</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>1.605414</v>
+        <v>0</v>
       </c>
       <c r="J59" s="3" t="n">
         <v>0</v>
@@ -4127,7 +4127,7 @@
         <v>0</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>4.326471</v>
+        <v>5.931885</v>
       </c>
       <c r="J61" s="3" t="n">
         <v>342.141501</v>
@@ -4660,16 +4660,16 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>0.037781</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>0.040164</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.040164</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>0.019674</v>
       </c>
       <c r="F70" s="3" t="n">
         <v>0</v>
@@ -4718,16 +4718,16 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>0.061314</v>
+        <v>0.099095</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0.292932</v>
+        <v>0.333096</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0.292932</v>
+        <v>0.333096</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0.423518</v>
+        <v>0.443192</v>
       </c>
       <c r="F71" s="3" t="n">
         <v>0.423518</v>
@@ -5274,16 +5274,16 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>0.3054659660294963</v>
+        <v>0.311999593258748</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>0.9875432723386401</v>
+        <v>0.9944046628208439</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.8688886233202016</v>
+        <v>0.8748660023249332</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>1.315446377234353</v>
+        <v>1.318518637661597</v>
       </c>
       <c r="F80" s="3" t="n">
         <v>1.684560558766177</v>
@@ -6667,37 +6667,37 @@
         <v>0</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>0</v>
+        <v>-0.162949</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>0</v>
+        <v>0.053498</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>0</v>
+        <v>-0.39149</v>
       </c>
       <c r="K103" s="3" t="n">
-        <v>0</v>
+        <v>-6.871244</v>
       </c>
       <c r="L103" s="3" t="n">
-        <v>0</v>
+        <v>3.518879</v>
       </c>
       <c r="M103" s="3" t="n">
-        <v>0</v>
+        <v>2.205996</v>
       </c>
       <c r="N103" s="3" t="n">
-        <v>0</v>
+        <v>-2.935221</v>
       </c>
       <c r="O103" s="3" t="n">
-        <v>0</v>
+        <v>-3.564686</v>
       </c>
       <c r="P103" s="3" t="n">
-        <v>0</v>
+        <v>-5.894138</v>
       </c>
       <c r="Q103" s="3" t="n">
-        <v>0</v>
+        <v>6.580996</v>
       </c>
       <c r="R103" s="3" t="n">
-        <v>0</v>
+        <v>-8.266534</v>
       </c>
     </row>
     <row r="104">
@@ -6859,19 +6859,19 @@
         <v>39.650754</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>-2.196569</v>
+        <v>-5.13179</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>-6.673419</v>
+        <v>-10.238105</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>-0.882026</v>
+        <v>-6.776164</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>0.172278</v>
+        <v>6.753274</v>
       </c>
       <c r="R106" s="3" t="n">
-        <v>-1.313637</v>
+        <v>-9.580171</v>
       </c>
     </row>
     <row r="107">
@@ -7712,13 +7712,13 @@
         <v>0</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>0</v>
+        <v>-0.057366</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>0</v>
+        <v>-0.025419</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>0</v>
+        <v>-0.00505</v>
       </c>
       <c r="H121" s="3" t="n">
         <v>0</v>
@@ -7727,10 +7727,10 @@
         <v>0</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>0</v>
+        <v>-0.07205</v>
       </c>
       <c r="K121" s="3" t="n">
-        <v>0</v>
+        <v>-0.499785</v>
       </c>
       <c r="L121" s="3" t="n">
         <v>0</v>
@@ -7739,13 +7739,13 @@
         <v>0</v>
       </c>
       <c r="N121" s="3" t="n">
-        <v>0</v>
+        <v>-3.953358</v>
       </c>
       <c r="O121" s="3" t="n">
-        <v>0</v>
+        <v>-10.625564</v>
       </c>
       <c r="P121" s="3" t="n">
-        <v>0</v>
+        <v>-21.562655</v>
       </c>
       <c r="Q121" s="3" t="n">
         <v>0</v>
@@ -8910,7 +8910,11 @@
           <t>Goodwill and intangible assets, net (Note 6)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>GoodwillAndOtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>-</t>
@@ -14900,7 +14904,11 @@
           <t>Goodwill and intangible assets, net (Note 7)</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>GoodwillAndOtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -15892,7 +15900,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -22776,7 +22784,11 @@
           <t>Current portion of finance lease obligations (Note 7) 7,476</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -24087,7 +24099,11 @@
           <t>Current portion of capital lease obligations (Note 8)</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E156" s="5" t="n">
         <v>0.037781</v>
       </c>
@@ -25301,7 +25317,11 @@
           <t>Deferred tax recovery (Note 11)</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E168" t="inlineStr">
         <is>
           <t>-</t>
@@ -26352,7 +26372,11 @@
           <t>Prepaid expenses and other current assets</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -29420,7 +29444,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
           <t>-</t>
@@ -30208,7 +30236,11 @@
           <t>Repurchase of common shares (Note 9)</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -31380,7 +31412,11 @@
           <t>Deferred tax recovery (Note 10)</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -32057,7 +32093,11 @@
           <t>Prepaid expenses and other current assets</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
@@ -33987,7 +34027,11 @@
           <t>Repurchase of common shares (Note 8)</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E258" t="inlineStr">
         <is>
           <t>-</t>
@@ -35072,7 +35116,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>-</t>
@@ -35658,7 +35706,11 @@
           <t>Repurchase of common shares</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -39420,7 +39472,11 @@
           <t>Purchase of common shares</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
           <t>-</t>
@@ -43218,7 +43274,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr"/>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E351" s="5" t="n">
         <v>-0.026191</v>
       </c>
@@ -53722,7 +53782,11 @@
           <t>Future income tax recovery (Note 12)</t>
         </is>
       </c>
-      <c r="D459" t="inlineStr"/>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E459" t="inlineStr">
         <is>
           <t>-</t>
@@ -54423,7 +54487,11 @@
           <t>Future income tax recovery (Note 11)</t>
         </is>
       </c>
-      <c r="D466" t="inlineStr"/>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E466" s="5" t="n">
         <v>-0.026191</v>
       </c>
